--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N54_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N54_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>55.57446786289317</v>
+        <v>9.030851027720139</v>
       </c>
       <c r="D2" t="n">
-        <v>54.96760140134859</v>
+        <v>8.932235227719145</v>
       </c>
       <c r="E2" t="n">
-        <v>16.2355574202989</v>
+        <v>2.638278080798571</v>
       </c>
       <c r="F2" t="n">
-        <v>16.17720334314612</v>
+        <v>2.628795543261245</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>52.20083252323257</v>
+        <v>8.482635285025292</v>
       </c>
       <c r="D3" t="n">
-        <v>51.36982595569324</v>
+        <v>8.347596717800153</v>
       </c>
       <c r="E3" t="n">
-        <v>16.2355574202989</v>
+        <v>2.638278080798571</v>
       </c>
       <c r="F3" t="n">
-        <v>16.17720334314612</v>
+        <v>2.628795543261245</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>21.8537450685479</v>
+        <v>3.551233573639034</v>
       </c>
       <c r="D4" t="n">
-        <v>22.63474548528818</v>
+        <v>3.678146141359329</v>
       </c>
       <c r="E4" t="n">
-        <v>16.2355574202989</v>
+        <v>2.638278080798571</v>
       </c>
       <c r="F4" t="n">
-        <v>16.17720334314612</v>
+        <v>2.628795543261245</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>52.18534915604963</v>
+        <v>8.480119237858066</v>
       </c>
       <c r="D5" t="n">
-        <v>52.6373703150125</v>
+        <v>8.553572676189532</v>
       </c>
       <c r="E5" t="n">
-        <v>16.2355574202989</v>
+        <v>2.638278080798571</v>
       </c>
       <c r="F5" t="n">
-        <v>16.17720334314612</v>
+        <v>2.628795543261245</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>52.16374583673678</v>
+        <v>8.476608698469727</v>
       </c>
       <c r="D6" t="n">
-        <v>52.74747626307245</v>
+        <v>8.571464892749274</v>
       </c>
       <c r="E6" t="n">
-        <v>16.2355574202989</v>
+        <v>2.638278080798571</v>
       </c>
       <c r="F6" t="n">
-        <v>16.17720334314612</v>
+        <v>2.628795543261245</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>56.16150424594656</v>
+        <v>9.126244439966316</v>
       </c>
       <c r="D7" t="n">
-        <v>56.39639293405546</v>
+        <v>9.164413851784012</v>
       </c>
       <c r="E7" t="n">
-        <v>16.2355574202989</v>
+        <v>2.638278080798571</v>
       </c>
       <c r="F7" t="n">
-        <v>16.17720334314612</v>
+        <v>2.628795543261245</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>45.22360856546314</v>
+        <v>7.34883639188776</v>
       </c>
       <c r="D8" t="n">
-        <v>45.58321625730198</v>
+        <v>7.407272641811573</v>
       </c>
       <c r="E8" t="n">
-        <v>16.2355574202989</v>
+        <v>2.638278080798571</v>
       </c>
       <c r="F8" t="n">
-        <v>16.17720334314612</v>
+        <v>2.628795543261245</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>40.96670662910496</v>
+        <v>6.657089827229555</v>
       </c>
       <c r="D9" t="n">
-        <v>40.55073869111167</v>
+        <v>6.589495037305646</v>
       </c>
       <c r="E9" t="n">
-        <v>16.2355574202989</v>
+        <v>2.638278080798571</v>
       </c>
       <c r="F9" t="n">
-        <v>16.17720334314612</v>
+        <v>2.628795543261245</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>19.91127897874334</v>
+        <v>3.235582834045793</v>
       </c>
       <c r="D10" t="n">
-        <v>19.74379158249653</v>
+        <v>3.208366132155686</v>
       </c>
       <c r="E10" t="n">
-        <v>16.2355574202989</v>
+        <v>2.638278080798571</v>
       </c>
       <c r="F10" t="n">
-        <v>16.17720334314612</v>
+        <v>2.628795543261245</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>40.75768272534788</v>
+        <v>6.623123442869032</v>
       </c>
       <c r="D11" t="n">
-        <v>41.66412869453298</v>
+        <v>6.77042091286161</v>
       </c>
       <c r="E11" t="n">
-        <v>16.2355574202989</v>
+        <v>2.638278080798571</v>
       </c>
       <c r="F11" t="n">
-        <v>16.17720334314612</v>
+        <v>2.628795543261245</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>20.98720675180559</v>
+        <v>3.410421097168409</v>
       </c>
       <c r="D12" t="n">
-        <v>20.40500452517329</v>
+        <v>3.31581323534066</v>
       </c>
       <c r="E12" t="n">
-        <v>16.2355574202989</v>
+        <v>2.638278080798571</v>
       </c>
       <c r="F12" t="n">
-        <v>16.17720334314612</v>
+        <v>2.628795543261245</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>43.71468145365434</v>
+        <v>7.103635736218831</v>
       </c>
       <c r="D13" t="n">
-        <v>42.53574576704764</v>
+        <v>6.912058687145242</v>
       </c>
       <c r="E13" t="n">
-        <v>16.2355574202989</v>
+        <v>2.638278080798571</v>
       </c>
       <c r="F13" t="n">
-        <v>16.17720334314612</v>
+        <v>2.628795543261245</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>8.369165658721336</v>
+        <v>1.359989419542217</v>
       </c>
       <c r="D14" t="n">
-        <v>9.256407623928737</v>
+        <v>1.50416623888842</v>
       </c>
       <c r="E14" t="n">
-        <v>16.2355574202989</v>
+        <v>2.638278080798571</v>
       </c>
       <c r="F14" t="n">
-        <v>16.17720334314612</v>
+        <v>2.628795543261245</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>9.065001870167597</v>
+        <v>1.473062803902235</v>
       </c>
       <c r="D15" t="n">
-        <v>8.531396404021358</v>
+        <v>1.386351915653471</v>
       </c>
       <c r="E15" t="n">
-        <v>16.2355574202989</v>
+        <v>2.638278080798571</v>
       </c>
       <c r="F15" t="n">
-        <v>16.17720334314612</v>
+        <v>2.628795543261245</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>42.72373848466784</v>
+        <v>6.942607503758524</v>
       </c>
       <c r="D16" t="n">
-        <v>42.66353520453953</v>
+        <v>6.932824470737674</v>
       </c>
       <c r="E16" t="n">
-        <v>16.2355574202989</v>
+        <v>2.638278080798571</v>
       </c>
       <c r="F16" t="n">
-        <v>16.17720334314612</v>
+        <v>2.628795543261245</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
